--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_rezjov_a_2020.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_rezjov_a_2020.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:07</t>
+    <t xml:space="preserve">2026-09-24 00:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -600,10 +600,10 @@
         <v>13</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -614,10 +614,10 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10">
@@ -631,7 +631,7 @@
         <v>-0.08</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11">
@@ -642,10 +642,10 @@
         <v>13</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.22</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12">
@@ -670,10 +670,10 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14">
@@ -684,10 +684,10 @@
         <v>19</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="15">
@@ -701,7 +701,7 @@
         <v>-0.01</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="16">

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_rezjov_a_2020.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_rezjov_a_2020.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:58</t>
+    <t xml:space="preserve">2026-10-01 23:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_rezjov_a_2020.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_rezjov_a_2020.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:04</t>
+    <t xml:space="preserve">2026-10-05 19:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
